--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daowen/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daowen/Documents/GitHub/Sarah-Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADC174FA-17EF-1745-B001-CD289600CB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CD19B0-6279-744B-A303-B8EB7062E096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="16720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="16720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unique Event" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="90">
   <si>
     <t>Event</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>School Holiday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The day following Chun Yeung Festival </t>
   </si>
 </sst>
 </file>
@@ -3086,7 +3089,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45B714B7-5F30-E84F-A193-CB7EFFD7934E}">
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -3111,10 +3114,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B3" s="63">
-        <v>46379</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -3122,7 +3125,7 @@
         <v>78</v>
       </c>
       <c r="B4" s="63">
-        <v>46380</v>
+        <v>46379</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -3130,7 +3133,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="63">
-        <v>46381</v>
+        <v>46380</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -3138,7 +3141,7 @@
         <v>78</v>
       </c>
       <c r="B6" s="63">
-        <v>46382</v>
+        <v>46381</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -3146,7 +3149,7 @@
         <v>78</v>
       </c>
       <c r="B7" s="63">
-        <v>46383</v>
+        <v>46382</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -3154,7 +3157,7 @@
         <v>78</v>
       </c>
       <c r="B8" s="63">
-        <v>46384</v>
+        <v>46383</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -3162,7 +3165,7 @@
         <v>78</v>
       </c>
       <c r="B9" s="63">
-        <v>46385</v>
+        <v>46384</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -3170,7 +3173,7 @@
         <v>78</v>
       </c>
       <c r="B10" s="63">
-        <v>46386</v>
+        <v>46385</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -3178,7 +3181,7 @@
         <v>78</v>
       </c>
       <c r="B11" s="63">
-        <v>46387</v>
+        <v>46386</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -3186,7 +3189,7 @@
         <v>78</v>
       </c>
       <c r="B12" s="63">
-        <v>46388</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -3194,23 +3197,23 @@
         <v>78</v>
       </c>
       <c r="B13" s="63">
-        <v>46389</v>
+        <v>46388</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B14" s="63">
-        <v>46405</v>
+        <v>46389</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B15" s="63">
-        <v>46421</v>
+        <v>46405</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -3218,7 +3221,7 @@
         <v>80</v>
       </c>
       <c r="B16" s="63">
-        <v>46422</v>
+        <v>46421</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -3226,7 +3229,7 @@
         <v>80</v>
       </c>
       <c r="B17" s="63">
-        <v>46423</v>
+        <v>46422</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -3234,7 +3237,7 @@
         <v>80</v>
       </c>
       <c r="B18" s="63">
-        <v>46424</v>
+        <v>46423</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -3242,7 +3245,7 @@
         <v>80</v>
       </c>
       <c r="B19" s="63">
-        <v>46425</v>
+        <v>46424</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -3250,7 +3253,7 @@
         <v>80</v>
       </c>
       <c r="B20" s="63">
-        <v>46426</v>
+        <v>46425</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -3258,7 +3261,7 @@
         <v>80</v>
       </c>
       <c r="B21" s="63">
-        <v>46427</v>
+        <v>46426</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -3266,7 +3269,7 @@
         <v>80</v>
       </c>
       <c r="B22" s="63">
-        <v>46428</v>
+        <v>46427</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -3274,7 +3277,7 @@
         <v>80</v>
       </c>
       <c r="B23" s="63">
-        <v>46429</v>
+        <v>46428</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -3282,15 +3285,15 @@
         <v>80</v>
       </c>
       <c r="B24" s="63">
-        <v>46430</v>
+        <v>46429</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B25" s="63">
-        <v>46468</v>
+        <v>46430</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -3298,7 +3301,7 @@
         <v>81</v>
       </c>
       <c r="B26" s="63">
-        <v>46469</v>
+        <v>46468</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -3306,7 +3309,7 @@
         <v>81</v>
       </c>
       <c r="B27" s="63">
-        <v>46470</v>
+        <v>46469</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -3314,7 +3317,7 @@
         <v>81</v>
       </c>
       <c r="B28" s="63">
-        <v>46471</v>
+        <v>46470</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -3322,7 +3325,7 @@
         <v>81</v>
       </c>
       <c r="B29" s="63">
-        <v>46472</v>
+        <v>46471</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -3330,7 +3333,7 @@
         <v>81</v>
       </c>
       <c r="B30" s="63">
-        <v>46473</v>
+        <v>46472</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -3338,7 +3341,7 @@
         <v>81</v>
       </c>
       <c r="B31" s="63">
-        <v>46474</v>
+        <v>46473</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
@@ -3346,7 +3349,7 @@
         <v>81</v>
       </c>
       <c r="B32" s="63">
-        <v>46475</v>
+        <v>46474</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -3354,7 +3357,7 @@
         <v>81</v>
       </c>
       <c r="B33" s="63">
-        <v>46476</v>
+        <v>46475</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -3362,7 +3365,7 @@
         <v>81</v>
       </c>
       <c r="B34" s="63">
-        <v>46477</v>
+        <v>46476</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -3370,7 +3373,7 @@
         <v>81</v>
       </c>
       <c r="B35" s="63">
-        <v>46478</v>
+        <v>46477</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -3378,23 +3381,23 @@
         <v>81</v>
       </c>
       <c r="B36" s="63">
-        <v>46479</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B37" s="63">
-        <v>46531</v>
+        <v>46479</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B38" s="63">
-        <v>46587</v>
+        <v>46531</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
@@ -3402,7 +3405,7 @@
         <v>83</v>
       </c>
       <c r="B39" s="63">
-        <v>46588</v>
+        <v>46587</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
@@ -3410,7 +3413,7 @@
         <v>83</v>
       </c>
       <c r="B40" s="63">
-        <v>46589</v>
+        <v>46588</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
@@ -3418,7 +3421,7 @@
         <v>83</v>
       </c>
       <c r="B41" s="63">
-        <v>46590</v>
+        <v>46589</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
@@ -3426,7 +3429,7 @@
         <v>83</v>
       </c>
       <c r="B42" s="63">
-        <v>46591</v>
+        <v>46590</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
@@ -3434,7 +3437,7 @@
         <v>83</v>
       </c>
       <c r="B43" s="63">
-        <v>46592</v>
+        <v>46591</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -3442,7 +3445,7 @@
         <v>83</v>
       </c>
       <c r="B44" s="63">
-        <v>46593</v>
+        <v>46592</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
@@ -3450,7 +3453,7 @@
         <v>83</v>
       </c>
       <c r="B45" s="63">
-        <v>46594</v>
+        <v>46593</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
@@ -3458,7 +3461,7 @@
         <v>83</v>
       </c>
       <c r="B46" s="63">
-        <v>46595</v>
+        <v>46594</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
@@ -3466,7 +3469,7 @@
         <v>83</v>
       </c>
       <c r="B47" s="63">
-        <v>46596</v>
+        <v>46595</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
@@ -3474,7 +3477,7 @@
         <v>83</v>
       </c>
       <c r="B48" s="63">
-        <v>46597</v>
+        <v>46596</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -3482,7 +3485,7 @@
         <v>83</v>
       </c>
       <c r="B49" s="63">
-        <v>46598</v>
+        <v>46597</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
@@ -3490,7 +3493,7 @@
         <v>83</v>
       </c>
       <c r="B50" s="63">
-        <v>46599</v>
+        <v>46598</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
@@ -3498,7 +3501,7 @@
         <v>83</v>
       </c>
       <c r="B51" s="63">
-        <v>46600</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
@@ -3506,7 +3509,7 @@
         <v>83</v>
       </c>
       <c r="B52" s="63">
-        <v>46601</v>
+        <v>46600</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
@@ -3514,7 +3517,7 @@
         <v>83</v>
       </c>
       <c r="B53" s="63">
-        <v>46602</v>
+        <v>46601</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
@@ -3522,7 +3525,7 @@
         <v>83</v>
       </c>
       <c r="B54" s="63">
-        <v>46603</v>
+        <v>46602</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
@@ -3530,7 +3533,7 @@
         <v>83</v>
       </c>
       <c r="B55" s="63">
-        <v>46604</v>
+        <v>46603</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
@@ -3538,7 +3541,7 @@
         <v>83</v>
       </c>
       <c r="B56" s="63">
-        <v>46605</v>
+        <v>46604</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
@@ -3546,7 +3549,7 @@
         <v>83</v>
       </c>
       <c r="B57" s="63">
-        <v>46606</v>
+        <v>46605</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
@@ -3554,7 +3557,7 @@
         <v>83</v>
       </c>
       <c r="B58" s="63">
-        <v>46607</v>
+        <v>46606</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
@@ -3562,7 +3565,7 @@
         <v>83</v>
       </c>
       <c r="B59" s="63">
-        <v>46608</v>
+        <v>46607</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
@@ -3570,7 +3573,7 @@
         <v>83</v>
       </c>
       <c r="B60" s="63">
-        <v>46609</v>
+        <v>46608</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
@@ -3578,7 +3581,7 @@
         <v>83</v>
       </c>
       <c r="B61" s="63">
-        <v>46610</v>
+        <v>46609</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
@@ -3586,7 +3589,7 @@
         <v>83</v>
       </c>
       <c r="B62" s="63">
-        <v>46611</v>
+        <v>46610</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
@@ -3594,7 +3597,7 @@
         <v>83</v>
       </c>
       <c r="B63" s="63">
-        <v>46612</v>
+        <v>46611</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
@@ -3602,7 +3605,7 @@
         <v>83</v>
       </c>
       <c r="B64" s="63">
-        <v>46613</v>
+        <v>46612</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
@@ -3610,7 +3613,7 @@
         <v>83</v>
       </c>
       <c r="B65" s="63">
-        <v>46614</v>
+        <v>46613</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
@@ -3618,7 +3621,7 @@
         <v>83</v>
       </c>
       <c r="B66" s="63">
-        <v>46615</v>
+        <v>46614</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
@@ -3626,7 +3629,7 @@
         <v>83</v>
       </c>
       <c r="B67" s="63">
-        <v>46616</v>
+        <v>46615</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
@@ -3634,7 +3637,7 @@
         <v>83</v>
       </c>
       <c r="B68" s="63">
-        <v>46617</v>
+        <v>46616</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
@@ -3642,7 +3645,7 @@
         <v>83</v>
       </c>
       <c r="B69" s="63">
-        <v>46618</v>
+        <v>46617</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
@@ -3650,7 +3653,7 @@
         <v>83</v>
       </c>
       <c r="B70" s="63">
-        <v>46619</v>
+        <v>46618</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
@@ -3658,7 +3661,7 @@
         <v>83</v>
       </c>
       <c r="B71" s="63">
-        <v>46620</v>
+        <v>46619</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
@@ -3666,7 +3669,7 @@
         <v>83</v>
       </c>
       <c r="B72" s="63">
-        <v>46621</v>
+        <v>46620</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
@@ -3674,7 +3677,7 @@
         <v>83</v>
       </c>
       <c r="B73" s="63">
-        <v>46622</v>
+        <v>46621</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
@@ -3682,7 +3685,7 @@
         <v>83</v>
       </c>
       <c r="B74" s="63">
-        <v>46623</v>
+        <v>46622</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
@@ -3690,7 +3693,7 @@
         <v>83</v>
       </c>
       <c r="B75" s="63">
-        <v>46624</v>
+        <v>46623</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
@@ -3698,7 +3701,7 @@
         <v>83</v>
       </c>
       <c r="B76" s="63">
-        <v>46625</v>
+        <v>46624</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
@@ -3706,7 +3709,7 @@
         <v>83</v>
       </c>
       <c r="B77" s="63">
-        <v>46626</v>
+        <v>46625</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
@@ -3714,7 +3717,7 @@
         <v>83</v>
       </c>
       <c r="B78" s="63">
-        <v>46627</v>
+        <v>46626</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
@@ -3722,7 +3725,7 @@
         <v>83</v>
       </c>
       <c r="B79" s="63">
-        <v>46628</v>
+        <v>46627</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
@@ -3730,7 +3733,7 @@
         <v>83</v>
       </c>
       <c r="B80" s="63">
-        <v>46629</v>
+        <v>46628</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
@@ -3738,6 +3741,14 @@
         <v>83</v>
       </c>
       <c r="B81" s="63">
+        <v>46629</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82" s="63">
         <v>46630</v>
       </c>
     </row>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CD19B0-6279-744B-A303-B8EB7062E096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="16720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="16720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unique Event" sheetId="1" r:id="rId1"/>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daowen/Documents/GitHub/Sarah-Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CD19B0-6279-744B-A303-B8EB7062E096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A59BA0A-CB4D-684F-9CC9-51F4C53393C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="16720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daowen/Documents/GitHub/Sarah-Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A59BA0A-CB4D-684F-9CC9-51F4C53393C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{431B4A43-D4A3-E748-AE32-64FA80BC59AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="16720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unique Event" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="91">
   <si>
     <t>Event</t>
   </si>
@@ -345,7 +345,10 @@
     <t>School Holiday</t>
   </si>
   <si>
-    <t xml:space="preserve">The day following Chun Yeung Festival </t>
+    <t>Monday after Chung Yeung Festival</t>
+  </si>
+  <si>
+    <t>Piano makup</t>
   </si>
 </sst>
 </file>
@@ -2124,7 +2127,7 @@
     </row>
     <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="43" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="B16" s="66">
         <v>46300</v>
@@ -2133,7 +2136,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D16" s="49">
-        <v>0.51041666666666663</v>
+        <v>0.53125</v>
       </c>
       <c r="E16" s="44"/>
       <c r="F16" s="44" t="s">
@@ -2146,7 +2149,7 @@
     </row>
     <row r="17" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="43" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="B17" s="66">
         <v>46306</v>
@@ -2168,7 +2171,7 @@
     </row>
     <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="43" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="B18" s="66">
         <v>46314</v>
@@ -2177,7 +2180,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D18" s="49">
-        <v>0.51041666666666663</v>
+        <v>0.53125</v>
       </c>
       <c r="E18" s="44"/>
       <c r="F18" s="44" t="s">
@@ -4153,7 +4156,7 @@
       </c>
       <c r="B11" s="16" t="str">
         <f ca="1"/>
-        <v>Piano Lesson</v>
+        <v>Piano makup</v>
       </c>
       <c r="C11" s="58">
         <f ca="1"/>
@@ -4799,7 +4802,7 @@
       </c>
       <c r="B28" s="16" t="str">
         <f ca="1"/>
-        <v>Piano Lesson</v>
+        <v>Piano makup</v>
       </c>
       <c r="C28" s="58">
         <f ca="1"/>
@@ -4807,7 +4810,7 @@
       </c>
       <c r="D28" s="58">
         <f ca="1"/>
-        <v>0.51041666666666663</v>
+        <v>0.53125</v>
       </c>
       <c r="E28" s="17">
         <f ca="1"/>
